--- a/data/nzd0255/nzd0255.xlsx
+++ b/data/nzd0255/nzd0255.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y391"/>
+  <dimension ref="A1:Y392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32137,6 +32137,87 @@
         <v>329.07</v>
       </c>
       <c r="Y391" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-02 21:54:02+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>260.81</v>
+      </c>
+      <c r="C392" t="n">
+        <v>252.79</v>
+      </c>
+      <c r="D392" t="n">
+        <v>251.96</v>
+      </c>
+      <c r="E392" t="n">
+        <v>269.73</v>
+      </c>
+      <c r="F392" t="n">
+        <v>289.87</v>
+      </c>
+      <c r="G392" t="n">
+        <v>282.82</v>
+      </c>
+      <c r="H392" t="n">
+        <v>289.53</v>
+      </c>
+      <c r="I392" t="n">
+        <v>291.87</v>
+      </c>
+      <c r="J392" t="n">
+        <v>287.02</v>
+      </c>
+      <c r="K392" t="n">
+        <v>292.05</v>
+      </c>
+      <c r="L392" t="n">
+        <v>315.49</v>
+      </c>
+      <c r="M392" t="n">
+        <v>327.74</v>
+      </c>
+      <c r="N392" t="n">
+        <v>324.33</v>
+      </c>
+      <c r="O392" t="n">
+        <v>323.36</v>
+      </c>
+      <c r="P392" t="n">
+        <v>331.76</v>
+      </c>
+      <c r="Q392" t="n">
+        <v>334.68</v>
+      </c>
+      <c r="R392" t="n">
+        <v>336.17</v>
+      </c>
+      <c r="S392" t="n">
+        <v>332.19</v>
+      </c>
+      <c r="T392" t="n">
+        <v>326.9</v>
+      </c>
+      <c r="U392" t="n">
+        <v>329.97</v>
+      </c>
+      <c r="V392" t="n">
+        <v>332.93</v>
+      </c>
+      <c r="W392" t="n">
+        <v>329.96</v>
+      </c>
+      <c r="X392" t="n">
+        <v>328.7</v>
+      </c>
+      <c r="Y392" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -32153,7 +32234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B392"/>
+  <dimension ref="A1:B393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36076,6 +36157,16 @@
       </c>
       <c r="B392" t="n">
         <v>-0.47</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2025-12-02 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>-0.66</v>
       </c>
     </row>
   </sheetData>
@@ -36244,28 +36335,28 @@
         <v>0.0362</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1301251407698167</v>
+        <v>0.1324893259032996</v>
       </c>
       <c r="J2" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K2" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02250792833397863</v>
+        <v>0.02342759686419704</v>
       </c>
       <c r="M2" t="n">
-        <v>5.154969087803042</v>
+        <v>5.152058689893089</v>
       </c>
       <c r="N2" t="n">
-        <v>39.46540787717846</v>
+        <v>39.41284023303641</v>
       </c>
       <c r="O2" t="n">
-        <v>6.282149940679422</v>
+        <v>6.277964656880158</v>
       </c>
       <c r="P2" t="n">
-        <v>253.0136122002801</v>
+        <v>252.989491695316</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36322,28 +36413,28 @@
         <v>0.0408</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1757606758879144</v>
+        <v>0.177973340945434</v>
       </c>
       <c r="J3" t="n">
+        <v>391</v>
+      </c>
+      <c r="K3" t="n">
         <v>390</v>
       </c>
-      <c r="K3" t="n">
-        <v>389</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.03545670074202334</v>
+        <v>0.03650695111492941</v>
       </c>
       <c r="M3" t="n">
-        <v>5.435585225903241</v>
+        <v>5.431059342742777</v>
       </c>
       <c r="N3" t="n">
-        <v>45.20780764226828</v>
+        <v>45.13438683558858</v>
       </c>
       <c r="O3" t="n">
-        <v>6.72367515888954</v>
+        <v>6.718213068635779</v>
       </c>
       <c r="P3" t="n">
-        <v>244.0710235147098</v>
+        <v>244.0484668089276</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36400,28 +36491,28 @@
         <v>0.036</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2827082725704504</v>
+        <v>0.284907710396053</v>
       </c>
       <c r="J4" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K4" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1012589721374528</v>
+        <v>0.1031494367974193</v>
       </c>
       <c r="M4" t="n">
-        <v>4.964839490295482</v>
+        <v>4.960492457816396</v>
       </c>
       <c r="N4" t="n">
-        <v>38.07102224017197</v>
+        <v>38.01551480961686</v>
       </c>
       <c r="O4" t="n">
-        <v>6.170171978168192</v>
+        <v>6.16567229177945</v>
       </c>
       <c r="P4" t="n">
-        <v>240.4509004140342</v>
+        <v>240.4284607369381</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36478,28 +36569,28 @@
         <v>0.0463</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3656642948674988</v>
+        <v>0.3649913892287751</v>
       </c>
       <c r="J5" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K5" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2884468391306371</v>
+        <v>0.2889190522562015</v>
       </c>
       <c r="M5" t="n">
-        <v>3.498301389868156</v>
+        <v>3.492740154870444</v>
       </c>
       <c r="N5" t="n">
-        <v>17.70203238264862</v>
+        <v>17.66067690613815</v>
       </c>
       <c r="O5" t="n">
-        <v>4.207378326541199</v>
+        <v>4.202460815538695</v>
       </c>
       <c r="P5" t="n">
-        <v>261.3421196804217</v>
+        <v>261.3489849734858</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36556,28 +36647,28 @@
         <v>0.0515</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3133600366502235</v>
+        <v>0.3145661255171649</v>
       </c>
       <c r="J6" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K6" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1850106410002251</v>
+        <v>0.1870312677794785</v>
       </c>
       <c r="M6" t="n">
-        <v>3.810373730302871</v>
+        <v>3.806231851552804</v>
       </c>
       <c r="N6" t="n">
-        <v>23.21447680627916</v>
+        <v>23.16769237175949</v>
       </c>
       <c r="O6" t="n">
-        <v>4.818140388809687</v>
+        <v>4.813282910006381</v>
       </c>
       <c r="P6" t="n">
-        <v>279.3943661660887</v>
+        <v>279.3820610923066</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36634,28 +36725,28 @@
         <v>0.052</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1284046684325524</v>
+        <v>0.1274533094719019</v>
       </c>
       <c r="J7" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K7" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04517819882647889</v>
+        <v>0.04478779602962635</v>
       </c>
       <c r="M7" t="n">
-        <v>3.636933555928216</v>
+        <v>3.631674594370869</v>
       </c>
       <c r="N7" t="n">
-        <v>18.70128689388913</v>
+        <v>18.6612895420045</v>
       </c>
       <c r="O7" t="n">
-        <v>4.32449845576214</v>
+        <v>4.319871472857091</v>
       </c>
       <c r="P7" t="n">
-        <v>281.1962709595179</v>
+        <v>281.2059771615441</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36712,28 +36803,28 @@
         <v>0.0679</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02037128156486476</v>
+        <v>0.02148995996586427</v>
       </c>
       <c r="J8" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K8" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001359339477799537</v>
+        <v>0.001520894333267742</v>
       </c>
       <c r="M8" t="n">
-        <v>3.262195014213277</v>
+        <v>3.258636816209007</v>
       </c>
       <c r="N8" t="n">
-        <v>16.36192768834823</v>
+        <v>16.33091051215376</v>
       </c>
       <c r="O8" t="n">
-        <v>4.04498797134778</v>
+        <v>4.041152126826428</v>
       </c>
       <c r="P8" t="n">
-        <v>286.9278318355018</v>
+        <v>286.9164185635281</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36790,28 +36881,28 @@
         <v>0.0546</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.06494711726298374</v>
+        <v>-0.06464661075262025</v>
       </c>
       <c r="J9" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K9" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01044724928026597</v>
+        <v>0.01041518222117843</v>
       </c>
       <c r="M9" t="n">
-        <v>3.705733022486722</v>
+        <v>3.697414765324239</v>
       </c>
       <c r="N9" t="n">
-        <v>21.44239057792617</v>
+        <v>21.38833213973166</v>
       </c>
       <c r="O9" t="n">
-        <v>4.630592897019363</v>
+        <v>4.624752116571402</v>
       </c>
       <c r="P9" t="n">
-        <v>293.0228698681208</v>
+        <v>293.0198039623793</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36868,28 +36959,28 @@
         <v>0.0931</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.06499359448551388</v>
+        <v>-0.06593404533481471</v>
       </c>
       <c r="J10" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K10" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01885159168119444</v>
+        <v>0.0194963571910145</v>
       </c>
       <c r="M10" t="n">
-        <v>2.623889919968573</v>
+        <v>2.622116122524749</v>
       </c>
       <c r="N10" t="n">
-        <v>11.79897396795353</v>
+        <v>11.77645101872039</v>
       </c>
       <c r="O10" t="n">
-        <v>3.434963459478649</v>
+        <v>3.431683408870986</v>
       </c>
       <c r="P10" t="n">
-        <v>290.4676720183042</v>
+        <v>290.4772669307575</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36946,28 +37037,28 @@
         <v>0.0654</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1170025827182171</v>
+        <v>-0.1186244726069909</v>
       </c>
       <c r="J11" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K11" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04950357025028873</v>
+        <v>0.05103708780437122</v>
       </c>
       <c r="M11" t="n">
-        <v>3.005733592867405</v>
+        <v>3.005447996759089</v>
       </c>
       <c r="N11" t="n">
-        <v>14.10656635574725</v>
+        <v>14.09325110485391</v>
       </c>
       <c r="O11" t="n">
-        <v>3.755870918408572</v>
+        <v>3.754097908266899</v>
       </c>
       <c r="P11" t="n">
-        <v>298.1267897714307</v>
+        <v>298.1433370386304</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37024,28 +37115,28 @@
         <v>0.0471</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1687140905396147</v>
+        <v>-0.1693921348753976</v>
       </c>
       <c r="J12" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K12" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1198428906799291</v>
+        <v>0.1213138063168472</v>
       </c>
       <c r="M12" t="n">
-        <v>2.633270316374595</v>
+        <v>2.629256772057627</v>
       </c>
       <c r="N12" t="n">
-        <v>11.21933424814626</v>
+        <v>11.19461863502271</v>
       </c>
       <c r="O12" t="n">
-        <v>3.349527466396755</v>
+        <v>3.345836014365126</v>
       </c>
       <c r="P12" t="n">
-        <v>321.1811190499848</v>
+        <v>321.1880367704017</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -37102,28 +37193,28 @@
         <v>0.0543</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.219254398257511</v>
+        <v>-0.2207298200735088</v>
       </c>
       <c r="J13" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K13" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2634951066629482</v>
+        <v>0.2668081130344363</v>
       </c>
       <c r="M13" t="n">
-        <v>2.104379201384372</v>
+        <v>2.105357113348948</v>
       </c>
       <c r="N13" t="n">
-        <v>7.211343144241649</v>
+        <v>7.211737070689019</v>
       </c>
       <c r="O13" t="n">
-        <v>2.68539441130007</v>
+        <v>2.685467756404649</v>
       </c>
       <c r="P13" t="n">
-        <v>336.2390245094818</v>
+        <v>336.254077441984</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37180,28 +37271,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2395774332191474</v>
+        <v>-0.2416333365090041</v>
       </c>
       <c r="J14" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K14" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2497581266912858</v>
+        <v>0.253399508722597</v>
       </c>
       <c r="M14" t="n">
-        <v>2.426212906673199</v>
+        <v>2.430465586963531</v>
       </c>
       <c r="N14" t="n">
-        <v>9.253157146887132</v>
+        <v>9.266067317498203</v>
       </c>
       <c r="O14" t="n">
-        <v>3.041900252619591</v>
+        <v>3.044021569814873</v>
       </c>
       <c r="P14" t="n">
-        <v>334.4340124315801</v>
+        <v>334.4549877032736</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37258,28 +37349,28 @@
         <v>0.0837</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2226469903367862</v>
+        <v>-0.2252128272894244</v>
       </c>
       <c r="J15" t="n">
+        <v>391</v>
+      </c>
+      <c r="K15" t="n">
         <v>390</v>
       </c>
-      <c r="K15" t="n">
-        <v>389</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.1656010122861173</v>
+        <v>0.1690651028295796</v>
       </c>
       <c r="M15" t="n">
-        <v>2.848343271783057</v>
+        <v>2.852522370972881</v>
       </c>
       <c r="N15" t="n">
-        <v>13.43665143258087</v>
+        <v>13.4593439016182</v>
       </c>
       <c r="O15" t="n">
-        <v>3.665603829191157</v>
+        <v>3.668697848231468</v>
       </c>
       <c r="P15" t="n">
-        <v>333.9657889987401</v>
+        <v>333.9919460662227</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37336,28 +37427,28 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.04775515436534709</v>
+        <v>-0.05000940103947849</v>
       </c>
       <c r="J16" t="n">
+        <v>391</v>
+      </c>
+      <c r="K16" t="n">
         <v>390</v>
       </c>
-      <c r="K16" t="n">
-        <v>389</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.01216689524256132</v>
+        <v>0.01335030342723709</v>
       </c>
       <c r="M16" t="n">
-        <v>2.594980533233086</v>
+        <v>2.597987532651333</v>
       </c>
       <c r="N16" t="n">
-        <v>9.960724448611309</v>
+        <v>9.979293027151893</v>
       </c>
       <c r="O16" t="n">
-        <v>3.156061540688221</v>
+        <v>3.159001903632205</v>
       </c>
       <c r="P16" t="n">
-        <v>337.1805678024147</v>
+        <v>337.2035484061966</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -37414,28 +37505,28 @@
         <v>0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.001095271332382537</v>
+        <v>-0.001193969185879248</v>
       </c>
       <c r="J17" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K17" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L17" t="n">
-        <v>7.121021910472258e-06</v>
+        <v>8.472292924333047e-06</v>
       </c>
       <c r="M17" t="n">
-        <v>2.510869759656075</v>
+        <v>2.513759526193089</v>
       </c>
       <c r="N17" t="n">
-        <v>9.040958538601933</v>
+        <v>9.063184929247209</v>
       </c>
       <c r="O17" t="n">
-        <v>3.006818674047694</v>
+        <v>3.010512403104696</v>
       </c>
       <c r="P17" t="n">
-        <v>338.8769014303163</v>
+        <v>338.900257315819</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -37492,28 +37583,28 @@
         <v>0.144</v>
       </c>
       <c r="I18" t="n">
-        <v>0.02696245236685621</v>
+        <v>0.02540216056355588</v>
       </c>
       <c r="J18" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K18" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L18" t="n">
-        <v>0.003907603757244749</v>
+        <v>0.003484105412908334</v>
       </c>
       <c r="M18" t="n">
-        <v>2.571756841121363</v>
+        <v>2.570575057692459</v>
       </c>
       <c r="N18" t="n">
-        <v>9.945447728431006</v>
+        <v>9.941078522938431</v>
       </c>
       <c r="O18" t="n">
-        <v>3.153640393011068</v>
+        <v>3.152947592799225</v>
       </c>
       <c r="P18" t="n">
-        <v>338.3455221363624</v>
+        <v>338.3614409515406</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -37570,28 +37661,28 @@
         <v>0.0881</v>
       </c>
       <c r="I19" t="n">
-        <v>0.08534125192660255</v>
+        <v>0.08442449391723725</v>
       </c>
       <c r="J19" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K19" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02651621903667178</v>
+        <v>0.02610877977557102</v>
       </c>
       <c r="M19" t="n">
-        <v>3.052846200572731</v>
+        <v>3.048524085764639</v>
       </c>
       <c r="N19" t="n">
-        <v>14.34998980303965</v>
+        <v>14.32056174623137</v>
       </c>
       <c r="O19" t="n">
-        <v>3.788138039068751</v>
+        <v>3.784251807984158</v>
       </c>
       <c r="P19" t="n">
-        <v>331.6396443115117</v>
+        <v>331.6489974987061</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -37648,28 +37739,28 @@
         <v>0.1203</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.01191353564696539</v>
+        <v>-0.01293801657064916</v>
       </c>
       <c r="J20" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K20" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0009465403056538868</v>
+        <v>0.001121812682874923</v>
       </c>
       <c r="M20" t="n">
-        <v>2.148647126728021</v>
+        <v>2.146932134685854</v>
       </c>
       <c r="N20" t="n">
-        <v>8.039839973333716</v>
+        <v>8.028359964695934</v>
       </c>
       <c r="O20" t="n">
-        <v>2.835461157084278</v>
+        <v>2.833436070338615</v>
       </c>
       <c r="P20" t="n">
-        <v>329.1091060924814</v>
+        <v>329.1195583184325</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -37726,28 +37817,28 @@
         <v>0.1085</v>
       </c>
       <c r="I21" t="n">
-        <v>0.05159025883941246</v>
+        <v>0.05130234153671694</v>
       </c>
       <c r="J21" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K21" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01684603367455439</v>
+        <v>0.01676220455027688</v>
       </c>
       <c r="M21" t="n">
-        <v>2.293816283845484</v>
+        <v>2.289334766422975</v>
       </c>
       <c r="N21" t="n">
-        <v>8.336346079023302</v>
+        <v>8.315742833872291</v>
       </c>
       <c r="O21" t="n">
-        <v>2.887273121653596</v>
+        <v>2.883702972546287</v>
       </c>
       <c r="P21" t="n">
-        <v>329.1391562517221</v>
+        <v>329.1420937165723</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -37804,28 +37895,28 @@
         <v>0.0973</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1116964212972419</v>
+        <v>0.112156456293651</v>
       </c>
       <c r="J22" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K22" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L22" t="n">
-        <v>0.05777959043014269</v>
+        <v>0.05856069749869341</v>
       </c>
       <c r="M22" t="n">
-        <v>2.571600806617461</v>
+        <v>2.567028335880768</v>
       </c>
       <c r="N22" t="n">
-        <v>10.91875237571913</v>
+        <v>10.89265850971166</v>
       </c>
       <c r="O22" t="n">
-        <v>3.304353548838128</v>
+        <v>3.300402779921212</v>
       </c>
       <c r="P22" t="n">
-        <v>329.1403431410115</v>
+        <v>329.1356496522244</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -37882,28 +37973,28 @@
         <v>0.0906</v>
       </c>
       <c r="I23" t="n">
-        <v>0.03691165450254727</v>
+        <v>0.03772825657067819</v>
       </c>
       <c r="J23" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K23" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L23" t="n">
-        <v>0.005809679354046082</v>
+        <v>0.00610273875055678</v>
       </c>
       <c r="M23" t="n">
-        <v>2.781896905488351</v>
+        <v>2.778335906757501</v>
       </c>
       <c r="N23" t="n">
-        <v>12.51298264757422</v>
+        <v>12.48675053900875</v>
       </c>
       <c r="O23" t="n">
-        <v>3.537369453078689</v>
+        <v>3.533659652401283</v>
       </c>
       <c r="P23" t="n">
-        <v>327.4813658648678</v>
+        <v>327.4730345146875</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -37960,28 +38051,28 @@
         <v>0.075</v>
       </c>
       <c r="I24" t="n">
-        <v>0.02843044352104776</v>
+        <v>0.02842480650405278</v>
       </c>
       <c r="J24" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K24" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L24" t="n">
-        <v>0.003013548028408919</v>
+        <v>0.003031050660259438</v>
       </c>
       <c r="M24" t="n">
-        <v>2.893465666008395</v>
+        <v>2.886088995679856</v>
       </c>
       <c r="N24" t="n">
-        <v>14.35141952398087</v>
+        <v>14.31471540119051</v>
       </c>
       <c r="O24" t="n">
-        <v>3.788326744617057</v>
+        <v>3.783479271938795</v>
       </c>
       <c r="P24" t="n">
-        <v>327.9664666368779</v>
+        <v>327.96652414832</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -38019,7 +38110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y391"/>
+  <dimension ref="A1:Y392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87667,6 +87758,133 @@
         </is>
       </c>
     </row>
+    <row r="392">
+      <c r="A392" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-02 21:54:02+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>-38.33352454414609,178.32547787476508</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>-38.33416865595325,178.325094226036</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>-38.33483171464991,178.32478901736772</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>-38.33557927501272,178.32467278122905</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>-38.3364178166565,178.32465658804276</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>-38.33721847396775,178.32463306919314</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>-38.337915576247696,178.3247661830938</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>-38.33863285434566,178.3248514645279</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>-38.339362900793034,178.3249071067083</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>-38.34005988754801,178.32509439519572</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>-38.34072474524296,178.32548787867304</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>-38.341403922860785,178.3257833100164</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>-38.34210484169924,178.32592526821847</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>-38.34280038436989,178.32609432148732</t>
+        </is>
+      </c>
+      <c r="P392" t="inlineStr">
+        <is>
+          <t>-38.343482465914654,178.3263879974968</t>
+        </is>
+      </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>-38.34415201265253,178.3267112487808</t>
+        </is>
+      </c>
+      <c r="R392" t="inlineStr">
+        <is>
+          <t>-38.34481459763019,178.32701515031192</t>
+        </is>
+      </c>
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>-38.345494301972806,178.32726056367952</t>
+        </is>
+      </c>
+      <c r="T392" t="inlineStr">
+        <is>
+          <t>-38.34617775228425,178.3274885566884</t>
+        </is>
+      </c>
+      <c r="U392" t="inlineStr">
+        <is>
+          <t>-38.346837085445884,178.3277991476303</t>
+        </is>
+      </c>
+      <c r="V392" t="inlineStr">
+        <is>
+          <t>-38.34750788069273,178.32811307522067</t>
+        </is>
+      </c>
+      <c r="W392" t="inlineStr">
+        <is>
+          <t>-38.348177483346284,178.32844858843276</t>
+        </is>
+      </c>
+      <c r="X392" t="inlineStr">
+        <is>
+          <t>-38.348822377893136,178.32882408809982</t>
+        </is>
+      </c>
+      <c r="Y392" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0255/nzd0255.xlsx
+++ b/data/nzd0255/nzd0255.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y392"/>
+  <dimension ref="A1:Y393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32220,6 +32220,87 @@
       <c r="Y392" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:54:11+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>263.89</v>
+      </c>
+      <c r="C393" t="n">
+        <v>255.04</v>
+      </c>
+      <c r="D393" t="n">
+        <v>253.42</v>
+      </c>
+      <c r="E393" t="n">
+        <v>268.96</v>
+      </c>
+      <c r="F393" t="n">
+        <v>288.88</v>
+      </c>
+      <c r="G393" t="n">
+        <v>280.89</v>
+      </c>
+      <c r="H393" t="n">
+        <v>288.31</v>
+      </c>
+      <c r="I393" t="n">
+        <v>292.07</v>
+      </c>
+      <c r="J393" t="n">
+        <v>287.15</v>
+      </c>
+      <c r="K393" t="n">
+        <v>293.59</v>
+      </c>
+      <c r="L393" t="n">
+        <v>315.8</v>
+      </c>
+      <c r="M393" t="n">
+        <v>327.31</v>
+      </c>
+      <c r="N393" t="n">
+        <v>323.67</v>
+      </c>
+      <c r="O393" t="n">
+        <v>322.9</v>
+      </c>
+      <c r="P393" t="n">
+        <v>330.46</v>
+      </c>
+      <c r="Q393" t="n">
+        <v>333.14</v>
+      </c>
+      <c r="R393" t="n">
+        <v>335.17</v>
+      </c>
+      <c r="S393" t="n">
+        <v>330.86</v>
+      </c>
+      <c r="T393" t="n">
+        <v>326.57</v>
+      </c>
+      <c r="U393" t="n">
+        <v>329.45</v>
+      </c>
+      <c r="V393" t="n">
+        <v>332.46</v>
+      </c>
+      <c r="W393" t="n">
+        <v>329.45</v>
+      </c>
+      <c r="X393" t="n">
+        <v>328.08</v>
+      </c>
+      <c r="Y393" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B393"/>
+  <dimension ref="A1:B394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36167,6 +36248,16 @@
       </c>
       <c r="B393" t="n">
         <v>-0.66</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>0.06</v>
       </c>
     </row>
   </sheetData>
@@ -36335,28 +36426,28 @@
         <v>0.0362</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1324893259032996</v>
+        <v>0.1364984380610809</v>
       </c>
       <c r="J2" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K2" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02342759686419704</v>
+        <v>0.02489749187580581</v>
       </c>
       <c r="M2" t="n">
-        <v>5.152058689893089</v>
+        <v>5.156115511926536</v>
       </c>
       <c r="N2" t="n">
-        <v>39.41284023303641</v>
+        <v>39.45081338228229</v>
       </c>
       <c r="O2" t="n">
-        <v>6.277964656880158</v>
+        <v>6.280988248857205</v>
       </c>
       <c r="P2" t="n">
-        <v>252.989491695316</v>
+        <v>252.9484086348515</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36413,28 +36504,28 @@
         <v>0.0408</v>
       </c>
       <c r="I3" t="n">
-        <v>0.177973340945434</v>
+        <v>0.1813765286536489</v>
       </c>
       <c r="J3" t="n">
+        <v>392</v>
+      </c>
+      <c r="K3" t="n">
         <v>391</v>
       </c>
-      <c r="K3" t="n">
-        <v>390</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.03650695111492941</v>
+        <v>0.03801010264258398</v>
       </c>
       <c r="M3" t="n">
-        <v>5.431059342742777</v>
+        <v>5.431452826515573</v>
       </c>
       <c r="N3" t="n">
-        <v>45.13438683558858</v>
+        <v>45.11907085857412</v>
       </c>
       <c r="O3" t="n">
-        <v>6.718213068635779</v>
+        <v>6.717073087184188</v>
       </c>
       <c r="P3" t="n">
-        <v>244.0484668089276</v>
+        <v>244.0136199733237</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36491,28 +36582,28 @@
         <v>0.036</v>
       </c>
       <c r="I4" t="n">
-        <v>0.284907710396053</v>
+        <v>0.2878632165000694</v>
       </c>
       <c r="J4" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K4" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1031494367974193</v>
+        <v>0.1054768082894811</v>
       </c>
       <c r="M4" t="n">
-        <v>4.960492457816396</v>
+        <v>4.959042932266382</v>
       </c>
       <c r="N4" t="n">
-        <v>38.01551480961686</v>
+        <v>37.99381437238162</v>
       </c>
       <c r="O4" t="n">
-        <v>6.16567229177945</v>
+        <v>6.163912261898414</v>
       </c>
       <c r="P4" t="n">
-        <v>240.4284607369381</v>
+        <v>240.398174421366</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36569,28 +36660,28 @@
         <v>0.0463</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3649913892287751</v>
+        <v>0.3638857411573307</v>
       </c>
       <c r="J5" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K5" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2889190522562015</v>
+        <v>0.288834464246466</v>
       </c>
       <c r="M5" t="n">
-        <v>3.492740154870444</v>
+        <v>3.489329437666241</v>
       </c>
       <c r="N5" t="n">
-        <v>17.66067690613815</v>
+        <v>17.62615923550579</v>
       </c>
       <c r="O5" t="n">
-        <v>4.202460815538695</v>
+        <v>4.198351966606158</v>
       </c>
       <c r="P5" t="n">
-        <v>261.3489849734858</v>
+        <v>261.3603150148476</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36647,28 +36738,28 @@
         <v>0.0515</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3145661255171649</v>
+        <v>0.3152057691611844</v>
       </c>
       <c r="J6" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K6" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1870312677794785</v>
+        <v>0.1885816161125532</v>
       </c>
       <c r="M6" t="n">
-        <v>3.806231851552804</v>
+        <v>3.799490347110523</v>
       </c>
       <c r="N6" t="n">
-        <v>23.16769237175949</v>
+        <v>23.11211709736743</v>
       </c>
       <c r="O6" t="n">
-        <v>4.813282910006381</v>
+        <v>4.807506328375183</v>
       </c>
       <c r="P6" t="n">
-        <v>279.3820610923066</v>
+        <v>279.3755063945409</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36725,28 +36816,28 @@
         <v>0.052</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1274533094719019</v>
+        <v>0.1254559094930412</v>
       </c>
       <c r="J7" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K7" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04478779602962635</v>
+        <v>0.04363913742447922</v>
       </c>
       <c r="M7" t="n">
-        <v>3.631674594370869</v>
+        <v>3.630920395088354</v>
       </c>
       <c r="N7" t="n">
-        <v>18.6612895420045</v>
+        <v>18.64806643457145</v>
       </c>
       <c r="O7" t="n">
-        <v>4.319871472857091</v>
+        <v>4.318340703855064</v>
       </c>
       <c r="P7" t="n">
-        <v>281.2059771615441</v>
+        <v>281.2264453602061</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36803,28 +36894,28 @@
         <v>0.0679</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02148995996586427</v>
+        <v>0.0219382974040044</v>
       </c>
       <c r="J8" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K8" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001520894333267742</v>
+        <v>0.001594672047366408</v>
       </c>
       <c r="M8" t="n">
-        <v>3.258636816209007</v>
+        <v>3.252218477920116</v>
       </c>
       <c r="N8" t="n">
-        <v>16.33091051215376</v>
+        <v>16.29098228936796</v>
       </c>
       <c r="O8" t="n">
-        <v>4.041152126826428</v>
+        <v>4.036208900610567</v>
       </c>
       <c r="P8" t="n">
-        <v>286.9164185635281</v>
+        <v>286.9118242610106</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36881,28 +36972,28 @@
         <v>0.0546</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.06464661075262025</v>
+        <v>-0.064234143233251</v>
       </c>
       <c r="J9" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K9" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01041518222117843</v>
+        <v>0.01034720834032821</v>
       </c>
       <c r="M9" t="n">
-        <v>3.697414765324239</v>
+        <v>3.689552464727929</v>
       </c>
       <c r="N9" t="n">
-        <v>21.38833213973166</v>
+        <v>21.33523623474595</v>
       </c>
       <c r="O9" t="n">
-        <v>4.624752116571402</v>
+        <v>4.619008144044124</v>
       </c>
       <c r="P9" t="n">
-        <v>293.0198039623793</v>
+        <v>293.0155772340237</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36959,28 +37050,28 @@
         <v>0.0931</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.06593404533481471</v>
+        <v>-0.06679096438132526</v>
       </c>
       <c r="J10" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K10" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0194963571910145</v>
+        <v>0.02010852897002335</v>
       </c>
       <c r="M10" t="n">
-        <v>2.622116122524749</v>
+        <v>2.619915244514518</v>
       </c>
       <c r="N10" t="n">
-        <v>11.77645101872039</v>
+        <v>11.75273729943546</v>
       </c>
       <c r="O10" t="n">
-        <v>3.431683408870986</v>
+        <v>3.428226553108102</v>
       </c>
       <c r="P10" t="n">
-        <v>290.4772669307575</v>
+        <v>290.4860481410643</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37037,28 +37128,28 @@
         <v>0.0654</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1186244726069909</v>
+        <v>-0.1193927360489568</v>
       </c>
       <c r="J11" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K11" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05103708780437122</v>
+        <v>0.05195549191671189</v>
       </c>
       <c r="M11" t="n">
-        <v>3.005447996759089</v>
+        <v>3.00124735212295</v>
       </c>
       <c r="N11" t="n">
-        <v>14.09325110485391</v>
+        <v>14.06238549407671</v>
       </c>
       <c r="O11" t="n">
-        <v>3.754097908266899</v>
+        <v>3.749984732512481</v>
       </c>
       <c r="P11" t="n">
-        <v>298.1433370386304</v>
+        <v>298.1512097576258</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37115,28 +37206,28 @@
         <v>0.0471</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1693921348753976</v>
+        <v>-0.1698839093619674</v>
       </c>
       <c r="J12" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K12" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1213138063168472</v>
+        <v>0.1225842796948342</v>
       </c>
       <c r="M12" t="n">
-        <v>2.629256772057627</v>
+        <v>2.624498886751765</v>
       </c>
       <c r="N12" t="n">
-        <v>11.19461863502271</v>
+        <v>11.16814511746826</v>
       </c>
       <c r="O12" t="n">
-        <v>3.345836014365126</v>
+        <v>3.341877483910542</v>
       </c>
       <c r="P12" t="n">
-        <v>321.1880367704017</v>
+        <v>321.1930761906452</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -37193,28 +37284,28 @@
         <v>0.0543</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2207298200735088</v>
+        <v>-0.2224132040148699</v>
       </c>
       <c r="J13" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K13" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2668081130344363</v>
+        <v>0.2703557969472795</v>
       </c>
       <c r="M13" t="n">
-        <v>2.105357113348948</v>
+        <v>2.107160310648192</v>
       </c>
       <c r="N13" t="n">
-        <v>7.211737070689019</v>
+        <v>7.217761163916588</v>
       </c>
       <c r="O13" t="n">
-        <v>2.685467756404649</v>
+        <v>2.686589131950881</v>
       </c>
       <c r="P13" t="n">
-        <v>336.254077441984</v>
+        <v>336.2713277860816</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37271,28 +37362,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2416333365090041</v>
+        <v>-0.2440140193164153</v>
       </c>
       <c r="J14" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K14" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L14" t="n">
-        <v>0.253399508722597</v>
+        <v>0.2573149177578432</v>
       </c>
       <c r="M14" t="n">
-        <v>2.430465586963531</v>
+        <v>2.436237384336655</v>
       </c>
       <c r="N14" t="n">
-        <v>9.266067317498203</v>
+        <v>9.291272909303649</v>
       </c>
       <c r="O14" t="n">
-        <v>3.044021569814873</v>
+        <v>3.048158937671008</v>
       </c>
       <c r="P14" t="n">
-        <v>334.4549877032736</v>
+        <v>334.4793835624749</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37349,28 +37440,28 @@
         <v>0.0837</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2252128272894244</v>
+        <v>-0.2279974577149057</v>
       </c>
       <c r="J15" t="n">
+        <v>392</v>
+      </c>
+      <c r="K15" t="n">
         <v>391</v>
       </c>
-      <c r="K15" t="n">
-        <v>390</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.1690651028295796</v>
+        <v>0.1727271203062355</v>
       </c>
       <c r="M15" t="n">
-        <v>2.852522370972881</v>
+        <v>2.857533186413586</v>
       </c>
       <c r="N15" t="n">
-        <v>13.4593439016182</v>
+        <v>13.4919514837461</v>
       </c>
       <c r="O15" t="n">
-        <v>3.668697848231468</v>
+        <v>3.673139186546856</v>
       </c>
       <c r="P15" t="n">
-        <v>333.9919460662227</v>
+        <v>334.0204592036027</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37427,28 +37518,28 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.05000940103947849</v>
+        <v>-0.05294479629353776</v>
       </c>
       <c r="J16" t="n">
+        <v>392</v>
+      </c>
+      <c r="K16" t="n">
         <v>391</v>
       </c>
-      <c r="K16" t="n">
-        <v>390</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.01335030342723709</v>
+        <v>0.01492170393267955</v>
       </c>
       <c r="M16" t="n">
-        <v>2.597987532651333</v>
+        <v>2.603760096536246</v>
       </c>
       <c r="N16" t="n">
-        <v>9.979293027151893</v>
+        <v>10.02825577917807</v>
       </c>
       <c r="O16" t="n">
-        <v>3.159001903632205</v>
+        <v>3.16674213967258</v>
       </c>
       <c r="P16" t="n">
-        <v>337.2035484061966</v>
+        <v>337.2336052953901</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -37505,28 +37596,28 @@
         <v>0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.001193969185879248</v>
+        <v>-0.004296542794175153</v>
       </c>
       <c r="J17" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K17" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L17" t="n">
-        <v>8.472292924333047e-06</v>
+        <v>0.0001093850686429976</v>
       </c>
       <c r="M17" t="n">
-        <v>2.513759526193089</v>
+        <v>2.519887843242069</v>
       </c>
       <c r="N17" t="n">
-        <v>9.063184929247209</v>
+        <v>9.123020608457841</v>
       </c>
       <c r="O17" t="n">
-        <v>3.010512403104696</v>
+        <v>3.020433844410078</v>
       </c>
       <c r="P17" t="n">
-        <v>338.900257315819</v>
+        <v>338.9320506940355</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -37583,28 +37674,28 @@
         <v>0.144</v>
       </c>
       <c r="I18" t="n">
-        <v>0.02540216056355588</v>
+        <v>0.02330749147817775</v>
       </c>
       <c r="J18" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K18" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L18" t="n">
-        <v>0.003484105412908334</v>
+        <v>0.002941983585611707</v>
       </c>
       <c r="M18" t="n">
-        <v>2.570575057692459</v>
+        <v>2.571150728799031</v>
       </c>
       <c r="N18" t="n">
-        <v>9.941078522938431</v>
+        <v>9.953531070025642</v>
       </c>
       <c r="O18" t="n">
-        <v>3.152947592799225</v>
+        <v>3.154921721695428</v>
       </c>
       <c r="P18" t="n">
-        <v>338.3614409515406</v>
+        <v>338.3829059076957</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -37661,28 +37752,28 @@
         <v>0.0881</v>
       </c>
       <c r="I19" t="n">
-        <v>0.08442449391723725</v>
+        <v>0.08278975864122971</v>
       </c>
       <c r="J19" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K19" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02610877977557102</v>
+        <v>0.0252466350893169</v>
       </c>
       <c r="M19" t="n">
-        <v>3.048524085764639</v>
+        <v>3.046876436033617</v>
       </c>
       <c r="N19" t="n">
-        <v>14.32056174623137</v>
+        <v>14.30705995560962</v>
       </c>
       <c r="O19" t="n">
-        <v>3.784251807984158</v>
+        <v>3.782467442769286</v>
       </c>
       <c r="P19" t="n">
-        <v>331.6489974987061</v>
+        <v>331.6657493194447</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -37739,28 +37830,28 @@
         <v>0.1203</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.01293801657064916</v>
+        <v>-0.01413378486440773</v>
       </c>
       <c r="J20" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K20" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L20" t="n">
-        <v>0.001121812682874923</v>
+        <v>0.001344785902863244</v>
       </c>
       <c r="M20" t="n">
-        <v>2.146932134685854</v>
+        <v>2.145811325277663</v>
       </c>
       <c r="N20" t="n">
-        <v>8.028359964695934</v>
+        <v>8.020201929385664</v>
       </c>
       <c r="O20" t="n">
-        <v>2.833436070338615</v>
+        <v>2.831996103349308</v>
       </c>
       <c r="P20" t="n">
-        <v>329.1195583184325</v>
+        <v>329.1318118596608</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -37817,28 +37908,28 @@
         <v>0.1085</v>
       </c>
       <c r="I21" t="n">
-        <v>0.05130234153671694</v>
+        <v>0.05073230098160755</v>
       </c>
       <c r="J21" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K21" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01676220455027688</v>
+        <v>0.01649354159198868</v>
       </c>
       <c r="M21" t="n">
-        <v>2.289334766422975</v>
+        <v>2.286203255187454</v>
       </c>
       <c r="N21" t="n">
-        <v>8.315742833872291</v>
+        <v>8.297329573958594</v>
       </c>
       <c r="O21" t="n">
-        <v>2.883702972546287</v>
+        <v>2.880508561688126</v>
       </c>
       <c r="P21" t="n">
-        <v>329.1420937165723</v>
+        <v>329.147935162177</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -37895,28 +37986,28 @@
         <v>0.0973</v>
       </c>
       <c r="I22" t="n">
-        <v>0.112156456293651</v>
+        <v>0.1123494595059531</v>
       </c>
       <c r="J22" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K22" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L22" t="n">
-        <v>0.05856069749869341</v>
+        <v>0.05909570770454886</v>
       </c>
       <c r="M22" t="n">
-        <v>2.567028335880768</v>
+        <v>2.561310476696925</v>
       </c>
       <c r="N22" t="n">
-        <v>10.89265850971166</v>
+        <v>10.86519213618669</v>
       </c>
       <c r="O22" t="n">
-        <v>3.300402779921212</v>
+        <v>3.296239089657589</v>
       </c>
       <c r="P22" t="n">
-        <v>329.1356496522244</v>
+        <v>329.1336718670369</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -37973,28 +38064,28 @@
         <v>0.0906</v>
       </c>
       <c r="I23" t="n">
-        <v>0.03772825657067819</v>
+        <v>0.03825669489343518</v>
       </c>
       <c r="J23" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K23" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L23" t="n">
-        <v>0.00610273875055678</v>
+        <v>0.006311708874310096</v>
       </c>
       <c r="M23" t="n">
-        <v>2.778335906757501</v>
+        <v>2.773520133871637</v>
       </c>
       <c r="N23" t="n">
-        <v>12.48675053900875</v>
+        <v>12.45730312021385</v>
       </c>
       <c r="O23" t="n">
-        <v>3.533659652401283</v>
+        <v>3.529490490171896</v>
       </c>
       <c r="P23" t="n">
-        <v>327.4730345146875</v>
+        <v>327.4676193846759</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -38051,28 +38142,28 @@
         <v>0.075</v>
       </c>
       <c r="I24" t="n">
-        <v>0.02842480650405278</v>
+        <v>0.02808139153722675</v>
       </c>
       <c r="J24" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K24" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L24" t="n">
-        <v>0.003031050660259438</v>
+        <v>0.002976762138487632</v>
       </c>
       <c r="M24" t="n">
-        <v>2.886088995679856</v>
+        <v>2.880140121002282</v>
       </c>
       <c r="N24" t="n">
-        <v>14.31471540119051</v>
+        <v>14.27921461776551</v>
       </c>
       <c r="O24" t="n">
-        <v>3.783479271938795</v>
+        <v>3.778784807020044</v>
       </c>
       <c r="P24" t="n">
-        <v>327.96652414832</v>
+        <v>327.9700432660925</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -38110,7 +38201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y392"/>
+  <dimension ref="A1:Y393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87885,6 +87976,133 @@
         </is>
       </c>
     </row>
+    <row r="393">
+      <c r="A393" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:54:11+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>-38.33353266308592,178.32551147642965</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>-38.33417458704677,178.32511877291554</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>-38.33483556329156,178.32480494570794</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>-38.335577560209195,178.32466426818064</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>-38.33641737649634,178.32464530413182</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>-38.337220226367045,178.32461115672515</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>-38.33791668400341,178.32475233156046</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>-38.33863262321702,178.32485372802563</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>-38.339362703791004,178.32490856907273</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>-38.34005738054688,178.32511167967854</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>-38.34072419795051,178.3254913476413</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>-38.34140478810002,178.32577852713464</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>-38.342106241832234,178.32591794860903</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>-38.34280140140628,178.32608923287933</t>
+        </is>
+      </c>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>-38.34348604541774,178.32637387396431</t>
+        </is>
+      </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>-38.3441569384268,178.32669482318906</t>
+        </is>
+      </c>
+      <c r="R393" t="inlineStr">
+        <is>
+          <t>-38.344817796208396,178.32700448426093</t>
+        </is>
+      </c>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>-38.3454985367712,178.32724636838967</t>
+        </is>
+      </c>
+      <c r="T393" t="inlineStr">
+        <is>
+          <t>-38.34617878693985,178.32748502684768</t>
+        </is>
+      </c>
+      <c r="U393" t="inlineStr">
+        <is>
+          <t>-38.34683869800951,178.32779357704655</t>
+        </is>
+      </c>
+      <c r="V393" t="inlineStr">
+        <is>
+          <t>-38.34750952928694,178.32810813617746</t>
+        </is>
+      </c>
+      <c r="W393" t="inlineStr">
+        <is>
+          <t>-38.348179541885756,178.32844338740142</t>
+        </is>
+      </c>
+      <c r="X393" t="inlineStr">
+        <is>
+          <t>-38.34882496014229,178.3288178171199</t>
+        </is>
+      </c>
+      <c r="Y393" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0255/nzd0255.xlsx
+++ b/data/nzd0255/nzd0255.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y393"/>
+  <dimension ref="A1:Y396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32301,6 +32301,249 @@
       <c r="Y393" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-27 21:54:07+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>266.03</v>
+      </c>
+      <c r="C394" t="n">
+        <v>258.34</v>
+      </c>
+      <c r="D394" t="n">
+        <v>255.6</v>
+      </c>
+      <c r="E394" t="n">
+        <v>270.99</v>
+      </c>
+      <c r="F394" t="n">
+        <v>290.45</v>
+      </c>
+      <c r="G394" t="n">
+        <v>280.89</v>
+      </c>
+      <c r="H394" t="n">
+        <v>289.64</v>
+      </c>
+      <c r="I394" t="n">
+        <v>291.39</v>
+      </c>
+      <c r="J394" t="n">
+        <v>283.01</v>
+      </c>
+      <c r="K394" t="n">
+        <v>294.92</v>
+      </c>
+      <c r="L394" t="n">
+        <v>315.58</v>
+      </c>
+      <c r="M394" t="n">
+        <v>326.2</v>
+      </c>
+      <c r="N394" t="n">
+        <v>323.85</v>
+      </c>
+      <c r="O394" t="n">
+        <v>321.42</v>
+      </c>
+      <c r="P394" t="n">
+        <v>329.77</v>
+      </c>
+      <c r="Q394" t="n">
+        <v>327.44</v>
+      </c>
+      <c r="R394" t="n">
+        <v>334.49</v>
+      </c>
+      <c r="S394" t="n">
+        <v>330.2</v>
+      </c>
+      <c r="T394" t="n">
+        <v>325.87</v>
+      </c>
+      <c r="U394" t="n">
+        <v>328.7</v>
+      </c>
+      <c r="V394" t="n">
+        <v>333.5</v>
+      </c>
+      <c r="W394" t="n">
+        <v>329.68</v>
+      </c>
+      <c r="X394" t="n">
+        <v>329.28</v>
+      </c>
+      <c r="Y394" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-04 21:53:55+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>265.91</v>
+      </c>
+      <c r="C395" t="n">
+        <v>257.32</v>
+      </c>
+      <c r="D395" t="n">
+        <v>253.7</v>
+      </c>
+      <c r="E395" t="n">
+        <v>270.99</v>
+      </c>
+      <c r="F395" t="n">
+        <v>290.04</v>
+      </c>
+      <c r="G395" t="n">
+        <v>280.41</v>
+      </c>
+      <c r="H395" t="n">
+        <v>288.43</v>
+      </c>
+      <c r="I395" t="n">
+        <v>290.84</v>
+      </c>
+      <c r="J395" t="n">
+        <v>282.82</v>
+      </c>
+      <c r="K395" t="n">
+        <v>294.67</v>
+      </c>
+      <c r="L395" t="n">
+        <v>314.77</v>
+      </c>
+      <c r="M395" t="n">
+        <v>325.66</v>
+      </c>
+      <c r="N395" t="n">
+        <v>322.71</v>
+      </c>
+      <c r="O395" t="n">
+        <v>321.19</v>
+      </c>
+      <c r="P395" t="n">
+        <v>328.69</v>
+      </c>
+      <c r="Q395" t="n">
+        <v>327.14</v>
+      </c>
+      <c r="R395" t="n">
+        <v>333.81</v>
+      </c>
+      <c r="S395" t="n">
+        <v>330</v>
+      </c>
+      <c r="T395" t="n">
+        <v>325.99</v>
+      </c>
+      <c r="U395" t="n">
+        <v>328.59</v>
+      </c>
+      <c r="V395" t="n">
+        <v>333.21</v>
+      </c>
+      <c r="W395" t="n">
+        <v>329.02</v>
+      </c>
+      <c r="X395" t="n">
+        <v>328.95</v>
+      </c>
+      <c r="Y395" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:53:48+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>265.96</v>
+      </c>
+      <c r="C396" t="n">
+        <v>257.23</v>
+      </c>
+      <c r="D396" t="n">
+        <v>253.43</v>
+      </c>
+      <c r="E396" t="n">
+        <v>273.9</v>
+      </c>
+      <c r="F396" t="n">
+        <v>290.85</v>
+      </c>
+      <c r="G396" t="n">
+        <v>284.9</v>
+      </c>
+      <c r="H396" t="n">
+        <v>287.94</v>
+      </c>
+      <c r="I396" t="n">
+        <v>291.19</v>
+      </c>
+      <c r="J396" t="n">
+        <v>283.18</v>
+      </c>
+      <c r="K396" t="n">
+        <v>296.49</v>
+      </c>
+      <c r="L396" t="n">
+        <v>314.76</v>
+      </c>
+      <c r="M396" t="n">
+        <v>326.58</v>
+      </c>
+      <c r="N396" t="n">
+        <v>323.77</v>
+      </c>
+      <c r="O396" t="n">
+        <v>322.01</v>
+      </c>
+      <c r="P396" t="n">
+        <v>328.7</v>
+      </c>
+      <c r="Q396" t="n">
+        <v>327.28</v>
+      </c>
+      <c r="R396" t="n">
+        <v>333.9</v>
+      </c>
+      <c r="S396" t="n">
+        <v>329.52</v>
+      </c>
+      <c r="T396" t="n">
+        <v>326.14</v>
+      </c>
+      <c r="U396" t="n">
+        <v>328.26</v>
+      </c>
+      <c r="V396" t="n">
+        <v>333.56</v>
+      </c>
+      <c r="W396" t="n">
+        <v>329.3</v>
+      </c>
+      <c r="X396" t="n">
+        <v>329.21</v>
+      </c>
+      <c r="Y396" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -32315,7 +32558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B394"/>
+  <dimension ref="A1:B397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36258,6 +36501,36 @@
       </c>
       <c r="B394" t="n">
         <v>0.06</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-01-27 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-02-04 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>0.64</v>
       </c>
     </row>
   </sheetData>
@@ -36426,28 +36699,28 @@
         <v>0.0362</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1364984380610809</v>
+        <v>0.1514735814998596</v>
       </c>
       <c r="J2" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K2" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02489749187580581</v>
+        <v>0.0305440778451247</v>
       </c>
       <c r="M2" t="n">
-        <v>5.156115511926536</v>
+        <v>5.181077497501384</v>
       </c>
       <c r="N2" t="n">
-        <v>39.45081338228229</v>
+        <v>39.804966103328</v>
       </c>
       <c r="O2" t="n">
-        <v>6.280988248857205</v>
+        <v>6.309117696106802</v>
       </c>
       <c r="P2" t="n">
-        <v>252.9484086348515</v>
+        <v>252.7945067902568</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36504,28 +36777,28 @@
         <v>0.0408</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1813765286536489</v>
+        <v>0.1954013495047855</v>
       </c>
       <c r="J3" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K3" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03801010264258398</v>
+        <v>0.04408971320632205</v>
       </c>
       <c r="M3" t="n">
-        <v>5.431452826515573</v>
+        <v>5.448151817975876</v>
       </c>
       <c r="N3" t="n">
-        <v>45.11907085857412</v>
+        <v>45.35275465208832</v>
       </c>
       <c r="O3" t="n">
-        <v>6.717073087184188</v>
+        <v>6.734445385634093</v>
       </c>
       <c r="P3" t="n">
-        <v>244.0136199733237</v>
+        <v>243.8696018685987</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36582,28 +36855,28 @@
         <v>0.036</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2878632165000694</v>
+        <v>0.2977581841534845</v>
       </c>
       <c r="J4" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K4" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1054768082894811</v>
+        <v>0.1131092722518192</v>
       </c>
       <c r="M4" t="n">
-        <v>4.959042932266382</v>
+        <v>4.958483273182712</v>
       </c>
       <c r="N4" t="n">
-        <v>37.99381437238162</v>
+        <v>37.9980877154724</v>
       </c>
       <c r="O4" t="n">
-        <v>6.163912261898414</v>
+        <v>6.164258894260721</v>
       </c>
       <c r="P4" t="n">
-        <v>240.398174421366</v>
+        <v>240.2964966458671</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36660,28 +36933,28 @@
         <v>0.0463</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3638857411573307</v>
+        <v>0.3654120061112041</v>
       </c>
       <c r="J5" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K5" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L5" t="n">
-        <v>0.288834464246466</v>
+        <v>0.2941543653525749</v>
       </c>
       <c r="M5" t="n">
-        <v>3.489329437666241</v>
+        <v>3.469808607499227</v>
       </c>
       <c r="N5" t="n">
-        <v>17.62615923550579</v>
+        <v>17.51307794094728</v>
       </c>
       <c r="O5" t="n">
-        <v>4.198351966606158</v>
+        <v>4.18486295366375</v>
       </c>
       <c r="P5" t="n">
-        <v>261.3603150148476</v>
+        <v>261.3446060839601</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36738,28 +37011,28 @@
         <v>0.0515</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3152057691611844</v>
+        <v>0.3195319500612188</v>
       </c>
       <c r="J6" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K6" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1885816161125532</v>
+        <v>0.1953172274940236</v>
       </c>
       <c r="M6" t="n">
-        <v>3.799490347110523</v>
+        <v>3.790425864313715</v>
       </c>
       <c r="N6" t="n">
-        <v>23.11211709736743</v>
+        <v>22.99191538120131</v>
       </c>
       <c r="O6" t="n">
-        <v>4.807506328375183</v>
+        <v>4.794988569454708</v>
       </c>
       <c r="P6" t="n">
-        <v>279.3755063945409</v>
+        <v>279.331041727757</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36816,28 +37089,28 @@
         <v>0.052</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1254559094930412</v>
+        <v>0.1215036498867995</v>
       </c>
       <c r="J7" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K7" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04363913742447922</v>
+        <v>0.04161657684145337</v>
       </c>
       <c r="M7" t="n">
-        <v>3.630920395088354</v>
+        <v>3.62228680997451</v>
       </c>
       <c r="N7" t="n">
-        <v>18.64806643457145</v>
+        <v>18.58292211915006</v>
       </c>
       <c r="O7" t="n">
-        <v>4.318340703855064</v>
+        <v>4.310791356485496</v>
       </c>
       <c r="P7" t="n">
-        <v>281.2264453602061</v>
+        <v>281.2670303717874</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36894,28 +37167,28 @@
         <v>0.0679</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0219382974040044</v>
+        <v>0.02380613113790322</v>
       </c>
       <c r="J8" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K8" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001594672047366408</v>
+        <v>0.001910711984720925</v>
       </c>
       <c r="M8" t="n">
-        <v>3.252218477920116</v>
+        <v>3.235311432546679</v>
       </c>
       <c r="N8" t="n">
-        <v>16.29098228936796</v>
+        <v>16.18133056627898</v>
       </c>
       <c r="O8" t="n">
-        <v>4.036208900610567</v>
+        <v>4.022602461874524</v>
       </c>
       <c r="P8" t="n">
-        <v>286.9118242610106</v>
+        <v>286.8926399640998</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36972,28 +37245,28 @@
         <v>0.0546</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.064234143233251</v>
+        <v>-0.0645070310910076</v>
       </c>
       <c r="J9" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K9" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01034720834032821</v>
+        <v>0.01062765020769252</v>
       </c>
       <c r="M9" t="n">
-        <v>3.689552464727929</v>
+        <v>3.663464275764181</v>
       </c>
       <c r="N9" t="n">
-        <v>21.33523623474595</v>
+        <v>21.17381163901115</v>
       </c>
       <c r="O9" t="n">
-        <v>4.619008144044124</v>
+        <v>4.6015010202119</v>
       </c>
       <c r="P9" t="n">
-        <v>293.0155772340237</v>
+        <v>293.0183824523523</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37050,28 +37323,28 @@
         <v>0.0931</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.06679096438132526</v>
+        <v>-0.07588987532162345</v>
       </c>
       <c r="J10" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K10" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02010852897002335</v>
+        <v>0.02576117780310938</v>
       </c>
       <c r="M10" t="n">
-        <v>2.619915244514518</v>
+        <v>2.64879528696459</v>
       </c>
       <c r="N10" t="n">
-        <v>11.75273729943546</v>
+        <v>11.90501138959095</v>
       </c>
       <c r="O10" t="n">
-        <v>3.428226553108102</v>
+        <v>3.450363950308858</v>
       </c>
       <c r="P10" t="n">
-        <v>290.4860481410643</v>
+        <v>290.5795576025084</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37128,28 +37401,28 @@
         <v>0.0654</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1193927360489568</v>
+        <v>-0.118793959362674</v>
       </c>
       <c r="J11" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K11" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05195549191671189</v>
+        <v>0.05235551666421256</v>
       </c>
       <c r="M11" t="n">
-        <v>3.00124735212295</v>
+        <v>2.983381658968277</v>
       </c>
       <c r="N11" t="n">
-        <v>14.06238549407671</v>
+        <v>13.96156568651528</v>
       </c>
       <c r="O11" t="n">
-        <v>3.749984732512481</v>
+        <v>3.736517855773644</v>
       </c>
       <c r="P11" t="n">
-        <v>298.1512097576258</v>
+        <v>298.1450429028604</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37206,28 +37479,28 @@
         <v>0.0471</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1698839093619674</v>
+        <v>-0.1725156798952137</v>
       </c>
       <c r="J12" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K12" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1225842796948342</v>
+        <v>0.1277748424900996</v>
       </c>
       <c r="M12" t="n">
-        <v>2.624498886751765</v>
+        <v>2.614847218523506</v>
       </c>
       <c r="N12" t="n">
-        <v>11.16814511746826</v>
+        <v>11.1045975292431</v>
       </c>
       <c r="O12" t="n">
-        <v>3.341877483910542</v>
+        <v>3.332356152820868</v>
       </c>
       <c r="P12" t="n">
-        <v>321.1930761906452</v>
+        <v>321.220128599679</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -37284,28 +37557,28 @@
         <v>0.0543</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2224132040148699</v>
+        <v>-0.2291491750666201</v>
       </c>
       <c r="J13" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K13" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2703557969472795</v>
+        <v>0.2823120793005172</v>
       </c>
       <c r="M13" t="n">
-        <v>2.107160310648192</v>
+        <v>2.120753504644542</v>
       </c>
       <c r="N13" t="n">
-        <v>7.217761163916588</v>
+        <v>7.296342166439609</v>
       </c>
       <c r="O13" t="n">
-        <v>2.686589131950881</v>
+        <v>2.701174219934658</v>
       </c>
       <c r="P13" t="n">
-        <v>336.2713277860816</v>
+        <v>336.3405506070682</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37362,28 +37635,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2440140193164153</v>
+        <v>-0.251290511127768</v>
       </c>
       <c r="J14" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K14" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2573149177578432</v>
+        <v>0.2690496694787387</v>
       </c>
       <c r="M14" t="n">
-        <v>2.436237384336655</v>
+        <v>2.454793643800403</v>
       </c>
       <c r="N14" t="n">
-        <v>9.291272909303649</v>
+        <v>9.37713143514552</v>
       </c>
       <c r="O14" t="n">
-        <v>3.048158937671008</v>
+        <v>3.062210220599742</v>
       </c>
       <c r="P14" t="n">
-        <v>334.4793835624749</v>
+        <v>334.55416406517</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37440,28 +37713,28 @@
         <v>0.0837</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2279974577149057</v>
+        <v>-0.2382455544775437</v>
       </c>
       <c r="J15" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K15" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1727271203062355</v>
+        <v>0.1850236309309949</v>
       </c>
       <c r="M15" t="n">
-        <v>2.857533186413586</v>
+        <v>2.882139808962485</v>
       </c>
       <c r="N15" t="n">
-        <v>13.4919514837461</v>
+        <v>13.69733633476296</v>
       </c>
       <c r="O15" t="n">
-        <v>3.673139186546856</v>
+        <v>3.700991263805274</v>
       </c>
       <c r="P15" t="n">
-        <v>334.0204592036027</v>
+        <v>334.1256949741838</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37518,28 +37791,28 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.05294479629353776</v>
+        <v>-0.06373782903999381</v>
       </c>
       <c r="J16" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K16" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01492170393267955</v>
+        <v>0.02116277087961427</v>
       </c>
       <c r="M16" t="n">
-        <v>2.603760096536246</v>
+        <v>2.630145158062727</v>
       </c>
       <c r="N16" t="n">
-        <v>10.02825577917807</v>
+        <v>10.29440320744641</v>
       </c>
       <c r="O16" t="n">
-        <v>3.16674213967258</v>
+        <v>3.208489240662403</v>
       </c>
       <c r="P16" t="n">
-        <v>337.2336052953901</v>
+        <v>337.3444494419156</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -37596,28 +37869,28 @@
         <v>0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.004296542794175153</v>
+        <v>-0.02266684008505224</v>
       </c>
       <c r="J17" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K17" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0001093850686429976</v>
+        <v>0.002789975699004077</v>
       </c>
       <c r="M17" t="n">
-        <v>2.519887843242069</v>
+        <v>2.576045098613648</v>
       </c>
       <c r="N17" t="n">
-        <v>9.123020608457841</v>
+        <v>10.03761644191228</v>
       </c>
       <c r="O17" t="n">
-        <v>3.020433844410078</v>
+        <v>3.168219759093786</v>
       </c>
       <c r="P17" t="n">
-        <v>338.9320506940355</v>
+        <v>339.1208463552489</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -37674,28 +37947,28 @@
         <v>0.144</v>
       </c>
       <c r="I18" t="n">
-        <v>0.02330749147817775</v>
+        <v>0.01545287502393739</v>
       </c>
       <c r="J18" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K18" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L18" t="n">
-        <v>0.002941983585611707</v>
+        <v>0.001295946152323868</v>
       </c>
       <c r="M18" t="n">
-        <v>2.571150728799031</v>
+        <v>2.577971428636284</v>
       </c>
       <c r="N18" t="n">
-        <v>9.953531070025642</v>
+        <v>10.05844534951626</v>
       </c>
       <c r="O18" t="n">
-        <v>3.154921721695428</v>
+        <v>3.171505218270382</v>
       </c>
       <c r="P18" t="n">
-        <v>338.3829059076957</v>
+        <v>338.4636329189794</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -37752,28 +38025,28 @@
         <v>0.0881</v>
       </c>
       <c r="I19" t="n">
-        <v>0.08278975864122971</v>
+        <v>0.07648619565310075</v>
       </c>
       <c r="J19" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K19" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0252466350893169</v>
+        <v>0.0218498314527209</v>
       </c>
       <c r="M19" t="n">
-        <v>3.046876436033617</v>
+        <v>3.047402438190489</v>
       </c>
       <c r="N19" t="n">
-        <v>14.30705995560962</v>
+        <v>14.31482302134072</v>
       </c>
       <c r="O19" t="n">
-        <v>3.782467442769286</v>
+        <v>3.783493494290789</v>
       </c>
       <c r="P19" t="n">
-        <v>331.6657493194447</v>
+        <v>331.7305373952399</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -37830,28 +38103,28 @@
         <v>0.1203</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.01413378486440773</v>
+        <v>-0.01852015690362891</v>
       </c>
       <c r="J20" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K20" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L20" t="n">
-        <v>0.001344785902863244</v>
+        <v>0.002333498228940578</v>
       </c>
       <c r="M20" t="n">
-        <v>2.145811325277663</v>
+        <v>2.145902280424421</v>
       </c>
       <c r="N20" t="n">
-        <v>8.020201929385664</v>
+        <v>8.015482277341023</v>
       </c>
       <c r="O20" t="n">
-        <v>2.831996103349308</v>
+        <v>2.831162707677011</v>
       </c>
       <c r="P20" t="n">
-        <v>329.1318118596608</v>
+        <v>329.1768894158255</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -37908,28 +38181,28 @@
         <v>0.1085</v>
       </c>
       <c r="I21" t="n">
-        <v>0.05073230098160755</v>
+        <v>0.04758509378514367</v>
       </c>
       <c r="J21" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K21" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01649354159198868</v>
+        <v>0.01475660311226623</v>
       </c>
       <c r="M21" t="n">
-        <v>2.286203255187454</v>
+        <v>2.28358070008969</v>
       </c>
       <c r="N21" t="n">
-        <v>8.297329573958594</v>
+        <v>8.263450221779102</v>
       </c>
       <c r="O21" t="n">
-        <v>2.880508561688126</v>
+        <v>2.874621752818812</v>
       </c>
       <c r="P21" t="n">
-        <v>329.147935162177</v>
+        <v>329.1802830246817</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -37986,28 +38259,28 @@
         <v>0.0973</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1123494595059531</v>
+        <v>0.1144366619115159</v>
       </c>
       <c r="J22" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K22" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L22" t="n">
-        <v>0.05909570770454886</v>
+        <v>0.06218227251867148</v>
       </c>
       <c r="M22" t="n">
-        <v>2.561310476696925</v>
+        <v>2.550768860223084</v>
       </c>
       <c r="N22" t="n">
-        <v>10.86519213618669</v>
+        <v>10.79554644744123</v>
       </c>
       <c r="O22" t="n">
-        <v>3.296239089657589</v>
+        <v>3.285657688719449</v>
       </c>
       <c r="P22" t="n">
-        <v>329.1336718670369</v>
+        <v>329.1122204448153</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -38064,28 +38337,28 @@
         <v>0.0906</v>
       </c>
       <c r="I23" t="n">
-        <v>0.03825669489343518</v>
+        <v>0.03961237346660611</v>
       </c>
       <c r="J23" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K23" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L23" t="n">
-        <v>0.006311708874310096</v>
+        <v>0.006886554083732954</v>
       </c>
       <c r="M23" t="n">
-        <v>2.773520133871637</v>
+        <v>2.758237533934203</v>
       </c>
       <c r="N23" t="n">
-        <v>12.45730312021385</v>
+        <v>12.3686143693388</v>
       </c>
       <c r="O23" t="n">
-        <v>3.529490490171896</v>
+        <v>3.516904088731849</v>
       </c>
       <c r="P23" t="n">
-        <v>327.4676193846759</v>
+        <v>327.453688850332</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -38142,28 +38415,28 @@
         <v>0.075</v>
       </c>
       <c r="I24" t="n">
-        <v>0.02808139153722675</v>
+        <v>0.02877279194937812</v>
       </c>
       <c r="J24" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K24" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L24" t="n">
-        <v>0.002976762138487632</v>
+        <v>0.00318273986598594</v>
       </c>
       <c r="M24" t="n">
-        <v>2.880140121002282</v>
+        <v>2.861882115261324</v>
       </c>
       <c r="N24" t="n">
-        <v>14.27921461776551</v>
+        <v>14.17231629138056</v>
       </c>
       <c r="O24" t="n">
-        <v>3.778784807020044</v>
+        <v>3.764613697496805</v>
       </c>
       <c r="P24" t="n">
-        <v>327.9700432660925</v>
+        <v>327.9629376748505</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -38201,7 +38474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y393"/>
+  <dimension ref="A1:Y396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88103,6 +88376,387 @@
         </is>
       </c>
     </row>
+    <row r="394">
+      <c r="A394" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-27 21:54:07+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>-38.33353830416146,178.3255348230446</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>-38.33418328597407,178.3251547750118</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>-38.33484130988923,178.32482872912283</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>-38.33558208105343,178.32468671167263</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>-38.33641807452759,178.32466319881885</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>-38.337220226367045,178.32461115672515</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>-38.33791547636801,178.3247674320025</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>-38.3386334090542,178.32484603213322</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>-38.33936897753909,178.32486199838596</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>-38.34005521540758,178.32512660718527</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>-38.340724586351605,178.32548888579288</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>-38.3414070216237,178.3257661806253</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>-38.34210585997782,178.32591994486617</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>-38.34280467360884,178.32607286083515</t>
+        </is>
+      </c>
+      <c r="P394" t="inlineStr">
+        <is>
+          <t>-38.34348794530717,178.32636637762715</t>
+        </is>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>-38.344175170169976,178.32663402714616</t>
+        </is>
+      </c>
+      <c r="R394" t="inlineStr">
+        <is>
+          <t>-38.34481997124107,178.32699723134562</t>
+        </is>
+      </c>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>-38.345500638249504,178.3272393241098</t>
+        </is>
+      </c>
+      <c r="T394" t="inlineStr">
+        <is>
+          <t>-38.34618098166352,178.3274775393064</t>
+        </is>
+      </c>
+      <c r="U394" t="inlineStr">
+        <is>
+          <t>-38.34684102382202,178.32778554255037</t>
+        </is>
+      </c>
+      <c r="V394" t="inlineStr">
+        <is>
+          <t>-38.34750588133354,178.32811906512381</t>
+        </is>
+      </c>
+      <c r="W394" t="inlineStr">
+        <is>
+          <t>-38.34817861352485,178.3284457329646</t>
+        </is>
+      </c>
+      <c r="X394" t="inlineStr">
+        <is>
+          <t>-38.34881996224043,178.32882995449998</t>
+        </is>
+      </c>
+      <c r="Y394" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-04 21:53:55+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>-38.333537987839605,178.32553351388853</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>-38.334180597215976,178.32514364709036</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>-38.334836301386964,178.32480800045832</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>-38.33558208105343,178.32468671167263</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>-38.33641789223944,178.32465852568404</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>-38.33722066219629,178.32460570699192</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>-38.337916575043906,178.3247536940064</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>-38.33863404465745,178.32483980751422</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>-38.33936926546429,178.32485986108367</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>-38.340055622388796,178.32512380126303</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>-38.34072601637345,178.32547982171423</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>-38.34140810820234,178.32576017421502</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>-38.34210827838853,178.3259073019038</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>-38.3428051821266,178.32607031653083</t>
+        </is>
+      </c>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>-38.343490919046246,178.32635464422904</t>
+        </is>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>-38.34417612973459,178.3266308273535</t>
+        </is>
+      </c>
+      <c r="R395" t="inlineStr">
+        <is>
+          <t>-38.3448221462733,178.32698997842985</t>
+        </is>
+      </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>-38.345501275061046,178.32723718947943</t>
+        </is>
+      </c>
+      <c r="T395" t="inlineStr">
+        <is>
+          <t>-38.34618060542521,178.32747882288493</t>
+        </is>
+      </c>
+      <c r="U395" t="inlineStr">
+        <is>
+          <t>-38.34684136494114,178.32778436415754</t>
+        </is>
+      </c>
+      <c r="V395" t="inlineStr">
+        <is>
+          <t>-38.347506898551416,178.3281160176293</t>
+        </is>
+      </c>
+      <c r="W395" t="inlineStr">
+        <is>
+          <t>-38.34818127751692,178.32843900221786</t>
+        </is>
+      </c>
+      <c r="X395" t="inlineStr">
+        <is>
+          <t>-38.348821336663555,178.32882661672065</t>
+        </is>
+      </c>
+      <c r="Y395" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:53:48+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>-38.33353811964038,178.32553405937023</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>-38.334180359972564,178.32514266521497</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>-38.33483558965212,178.32480505480618</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>-38.33558856166461,178.32471888436714</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>-38.33641825236951,178.32466775797482</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>-38.3372165853671,178.32465668470098</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>-38.33791701996177,178.3247481306855</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>-38.338633640182685,178.32484376863542</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>-38.339368719921765,178.32486391070904</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>-38.34005265956405,178.32514422837596</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>-38.34072603402803,178.32547970981202</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>-38.34140625699412,178.3257704073583</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>-38.34210602969089,178.3259190576408</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>-38.342803369149976,178.32607938752864</t>
+        </is>
+      </c>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>-38.34349089151162,178.32635475287162</t>
+        </is>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>-38.344175681937784,178.32663232059008</t>
+        </is>
+      </c>
+      <c r="R396" t="inlineStr">
+        <is>
+          <t>-38.34482185840142,178.32699093837462</t>
+        </is>
+      </c>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>-38.34550280340854,178.3272320663664</t>
+        </is>
+      </c>
+      <c r="T396" t="inlineStr">
+        <is>
+          <t>-38.346180135127305,178.3274804273581</t>
+        </is>
+      </c>
+      <c r="U396" t="inlineStr">
+        <is>
+          <t>-38.346842388298434,178.32778082897897</t>
+        </is>
+      </c>
+      <c r="V396" t="inlineStr">
+        <is>
+          <t>-38.347505670874654,178.3281196956399</t>
+        </is>
+      </c>
+      <c r="W396" t="inlineStr">
+        <is>
+          <t>-38.34818014733851,178.32844185768624</t>
+        </is>
+      </c>
+      <c r="X396" t="inlineStr">
+        <is>
+          <t>-38.34882025378472,178.32882924648618</t>
+        </is>
+      </c>
+      <c r="Y396" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
